--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\systemoneid\aspect\api\placeholders\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6470" tabRatio="815"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6465" tabRatio="815"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="6" r:id="rId1"/>
+    <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="144525" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" Flags="2"/>
@@ -24,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Total Tests</t>
   </si>
@@ -41,88 +36,49 @@
     <t>RIF Resistance Rate</t>
   </si>
   <si>
-    <t>Date Range: 9/1/2017 - 9/28/2019</t>
-  </si>
-  <si>
     <t>State</t>
   </si>
   <si>
     <t>County</t>
   </si>
   <si>
-    <t>Shelburne Falls ML</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Hampshire County</t>
-  </si>
-  <si>
-    <t>Akron ML</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Summit County</t>
-  </si>
-  <si>
-    <t>Boston Micro</t>
-  </si>
-  <si>
-    <t>Suffolk County</t>
-  </si>
-  <si>
-    <t>Philadelphia ML</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t>Philadelphia County</t>
-  </si>
-  <si>
-    <t>Pittsburgh ML</t>
-  </si>
-  <si>
-    <t>Allegheny County</t>
-  </si>
-  <si>
-    <t>Northampton ML</t>
-  </si>
-  <si>
-    <t>Wooster ML</t>
-  </si>
-  <si>
-    <t>Wayne County</t>
-  </si>
-  <si>
-    <t>Atlanta ML</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Fulton County</t>
-  </si>
-  <si>
-    <t>Cleveland ML</t>
-  </si>
-  <si>
-    <t>Cuyahoga County</t>
-  </si>
-  <si>
-    <t>Wooster Hospital</t>
-  </si>
-  <si>
     <t>Devices</t>
+  </si>
+  <si>
+    <t>Date Range: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>States: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>LGA: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
+  </si>
+  <si>
+    <t>&lt;state&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalResults&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalResult1&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalResult2&gt;</t>
+  </si>
+  <si>
+    <t>&lt;rifResistance&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -273,7 +229,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -289,138 +245,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="29" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="31" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="33" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="35" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="37" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="39" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="41" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="32" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="34" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="36" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="38" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="40" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -758,287 +630,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="27.08203125" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="3" customWidth="1"/>
-    <col min="5" max="6" width="14.83203125" customWidth="1"/>
+    <col min="1" max="3" width="27.125" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
+    <col min="5" max="6" width="14.875" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="38" t="s">
+    <row r="7" spans="1:7" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1927</v>
-      </c>
-      <c r="E8" s="5">
-        <v>200</v>
-      </c>
-      <c r="F8" s="5">
-        <v>164</v>
-      </c>
-      <c r="G8" s="37">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="9">
-        <v>45</v>
-      </c>
-      <c r="E9" s="10">
-        <v>9</v>
-      </c>
-      <c r="F9" s="11">
-        <v>7</v>
-      </c>
-      <c r="G9" s="37">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="33" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="E8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="12">
-        <v>1011</v>
-      </c>
-      <c r="E10" s="13">
-        <v>123</v>
-      </c>
-      <c r="F10" s="14">
-        <v>100</v>
-      </c>
-      <c r="G10" s="37">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
+      <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="G8" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="15">
-        <v>24</v>
-      </c>
-      <c r="E11" s="16">
-        <v>11</v>
-      </c>
-      <c r="F11" s="17">
-        <v>9</v>
-      </c>
-      <c r="G11" s="37">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="18">
-        <v>2130</v>
-      </c>
-      <c r="E12" s="19">
-        <v>309</v>
-      </c>
-      <c r="F12" s="20">
-        <v>274</v>
-      </c>
-      <c r="G12" s="37">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="21">
-        <v>2063</v>
-      </c>
-      <c r="E13" s="22">
-        <v>348</v>
-      </c>
-      <c r="F13" s="23">
-        <v>319</v>
-      </c>
-      <c r="G13" s="37">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="24">
-        <v>2653</v>
-      </c>
-      <c r="E14" s="25">
-        <v>329</v>
-      </c>
-      <c r="F14" s="26">
-        <v>295</v>
-      </c>
-      <c r="G14" s="37">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="27">
-        <v>5</v>
-      </c>
-      <c r="E15" s="28">
-        <v>1</v>
-      </c>
-      <c r="F15" s="29">
-        <v>1</v>
-      </c>
-      <c r="G15" s="37">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="30">
-        <v>4</v>
-      </c>
-      <c r="E16" s="31">
-        <v>2</v>
-      </c>
-      <c r="F16" s="32">
-        <v>2</v>
-      </c>
-      <c r="G16" s="37">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="34">
-        <v>44</v>
-      </c>
-      <c r="E17" s="35">
-        <v>30</v>
-      </c>
-      <c r="F17" s="36">
-        <v>30</v>
-      </c>
-      <c r="G17" s="37">
-        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Total Tests</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>&lt;rifResistance&gt;</t>
+  </si>
+  <si>
+    <t>&lt;county&gt;</t>
   </si>
 </sst>
 </file>
@@ -704,7 +707,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>14</v>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Total Tests</t>
   </si>
@@ -66,16 +66,13 @@
     <t>&lt;totalResults&gt;</t>
   </si>
   <si>
-    <t>&lt;totalResult1&gt;</t>
+    <t>&lt;county&gt;</t>
   </si>
   <si>
-    <t>&lt;totalResult2&gt;</t>
+    <t>&lt;totalDetected2&gt;</t>
   </si>
   <si>
-    <t>&lt;rifResistance&gt;</t>
-  </si>
-  <si>
-    <t>&lt;county&gt;</t>
+    <t>&lt;totalDetected1&gt;</t>
   </si>
 </sst>
 </file>
@@ -633,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G756"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="27.125" customWidth="1"/>
@@ -707,19 +704,4508 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>17</v>
+      <c r="G8" s="7" t="e">
+        <f t="shared" ref="G8:G72" si="0">IF(F8=0,0,E8/F8)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G27" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G28" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G29" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G30" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G31" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G32" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G33" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G37" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G38" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G40" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G41" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G42" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G45" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G46" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G48" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G50" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G51" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G52" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G54" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G55" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G56" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G58" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G59" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G60" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G61" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G62" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G63" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G66" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G67" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G71" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G72" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G73" s="7">
+        <f t="shared" ref="G73:G136" si="1">IF(F73=0,0,E73/F73)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G74" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G76" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G77" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G78" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G79" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G80" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G81" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G83" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G84" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G85" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G86" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G88" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G89" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G95" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G96" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G97" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G98" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G99" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G100" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G101" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G102" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G103" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G104" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G105" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G106" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G107" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G108" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G109" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G110" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G111" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G112" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G113" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G114" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G115" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G116" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G117" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G118" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G119" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G120" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G121" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G122" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G123" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G124" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G125" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G126" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G127" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G128" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G129" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G130" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G131" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G132" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G133" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G134" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G135" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G136" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G137" s="7">
+        <f t="shared" ref="G137:G200" si="2">IF(F137=0,0,E137/F137)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G138" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G139" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G140" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G141" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G142" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G143" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G144" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G145" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G146" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G147" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G148" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G149" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G150" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G151" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G152" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G153" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G154" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G155" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G156" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G157" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G158" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G159" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G160" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G161" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G162" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G163" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G164" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G165" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G166" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G167" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G168" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G169" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G170" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G171" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G172" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G173" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G174" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G175" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G176" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G177" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G178" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G179" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G180" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G181" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G182" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G183" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G184" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G185" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G186" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G187" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G188" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G189" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G190" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G191" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G192" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G193" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G194" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G195" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G196" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G197" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G198" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G199" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G200" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G201" s="7">
+        <f t="shared" ref="G201:G264" si="3">IF(F201=0,0,E201/F201)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G202" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G203" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G204" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G205" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G206" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G207" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G208" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G209" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G210" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G211" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G212" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G213" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G214" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G215" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G216" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G217" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G218" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G219" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G220" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G221" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G222" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G223" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G224" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G225" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G226" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G227" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G228" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G229" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G230" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G231" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G232" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G233" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G234" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G235" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G236" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G237" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G238" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G239" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G240" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G241" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G242" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G243" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G244" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G245" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G246" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G247" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G248" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G249" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G250" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G251" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G252" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G253" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G254" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G255" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G256" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G257" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G258" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G259" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G260" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G261" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G262" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G263" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G264" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G265" s="7">
+        <f t="shared" ref="G265:G328" si="4">IF(F265=0,0,E265/F265)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G266" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G267" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G268" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G269" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G270" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G271" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G272" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G273" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G274" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G275" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G276" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G277" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G278" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G279" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G280" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G281" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G282" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G283" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G284" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G285" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G286" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G287" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G288" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G289" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G290" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G291" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G292" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G293" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G294" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G295" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G296" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G297" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G298" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G299" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G300" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G301" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G302" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G303" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G304" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G305" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G306" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G307" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G308" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G309" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G310" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G311" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G312" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G313" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G314" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G315" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G316" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G317" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G318" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G319" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G320" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G321" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G322" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G323" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G324" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G325" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G326" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G327" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G328" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G329" s="7">
+        <f t="shared" ref="G329:G392" si="5">IF(F329=0,0,E329/F329)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G330" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G331" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G332" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G333" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G334" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G335" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G336" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G337" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G338" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G339" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G340" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G341" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G342" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G343" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G344" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G345" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G346" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G347" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G348" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G349" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G350" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G351" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G352" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G353" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G354" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G355" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G356" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G357" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G358" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G359" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G360" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G361" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G362" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G363" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G364" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G365" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G366" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G367" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G368" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G369" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G370" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G371" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G372" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G373" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G374" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G375" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G376" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G377" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G378" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G379" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G380" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G381" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G382" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G383" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G384" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G385" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G386" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G387" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G388" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G389" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G390" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G391" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G392" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G393" s="7">
+        <f t="shared" ref="G393:G456" si="6">IF(F393=0,0,E393/F393)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G394" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G395" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G396" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G397" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G398" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G399" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G400" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G401" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G402" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G403" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G404" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G405" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G406" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G407" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G408" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G409" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G410" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G411" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G412" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G413" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G414" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G415" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G416" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G417" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G418" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G419" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G420" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G421" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G422" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G423" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G424" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G425" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G426" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G427" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G428" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G429" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G430" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G431" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G432" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G433" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G434" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G435" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G436" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G437" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G438" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G439" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G440" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G441" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G442" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G443" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G444" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G445" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G446" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G447" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G448" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G449" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G450" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G451" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G452" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G453" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G454" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G455" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G456" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G457" s="7">
+        <f t="shared" ref="G457:G520" si="7">IF(F457=0,0,E457/F457)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G458" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G459" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G460" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G461" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G462" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G463" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G464" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G465" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G466" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G467" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G468" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G469" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G470" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G471" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G472" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G473" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G474" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G475" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G476" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G477" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G478" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G479" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G480" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G481" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G482" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G483" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G484" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G485" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G486" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G487" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G488" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G489" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G490" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G491" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G492" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G493" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G494" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G495" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G496" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G497" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G498" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G499" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G500" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G501" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G502" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G503" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G504" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G505" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G506" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G507" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G508" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G509" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G510" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G511" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G512" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G513" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G514" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G515" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G516" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G517" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G518" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G519" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G520" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G521" s="7">
+        <f t="shared" ref="G521:G584" si="8">IF(F521=0,0,E521/F521)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G522" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G523" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G524" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G525" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G526" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G527" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G528" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G529" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G530" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G531" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G532" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G533" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G534" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G535" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G536" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G537" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G538" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G539" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G540" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G541" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G542" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G543" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G544" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G545" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G546" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G547" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G548" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G549" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G550" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G551" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G552" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G553" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G554" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G555" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G556" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G557" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G558" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G559" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G560" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G561" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G562" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G563" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G564" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G565" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G566" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G567" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G568" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G569" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G570" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G571" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G572" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G573" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G574" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G575" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G576" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G577" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G578" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G579" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G580" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G581" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G582" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G583" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G584" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G585" s="7">
+        <f t="shared" ref="G585:G648" si="9">IF(F585=0,0,E585/F585)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G586" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G587" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G588" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G589" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G590" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G591" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G592" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G593" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G594" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G595" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G596" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G597" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G598" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G599" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G600" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G601" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G602" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G603" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G604" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G605" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G606" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G607" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G608" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G609" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G610" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G611" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G612" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G613" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G614" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G615" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G616" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G617" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G618" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G619" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G620" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G621" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G622" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G623" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G624" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G625" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G626" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G627" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G628" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G629" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G630" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G631" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G632" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G633" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G634" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G635" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G636" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G637" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G638" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G639" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G640" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G641" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G642" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G643" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G644" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G645" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G646" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G647" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G648" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G649" s="7">
+        <f t="shared" ref="G649:G712" si="10">IF(F649=0,0,E649/F649)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G650" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G651" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G652" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G653" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G654" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G655" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G656" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G657" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G658" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G659" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G660" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G661" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G662" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G663" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G664" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G665" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G666" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G667" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G668" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G669" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G670" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G671" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G672" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G673" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G674" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G675" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G676" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G677" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G678" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G679" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G680" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G681" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G682" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G683" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G684" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G685" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G686" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G687" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G688" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G689" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G690" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G691" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G692" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G693" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G694" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G695" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G696" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G697" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G698" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G699" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G700" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G701" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G702" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G703" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G704" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G705" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G706" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G707" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G708" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G709" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G710" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G711" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G712" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G713" s="7">
+        <f t="shared" ref="G713:G756" si="11">IF(F713=0,0,E713/F713)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G714" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G715" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G716" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G717" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G718" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G719" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G720" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G721" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G722" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G723" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G724" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G725" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G726" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G727" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G728" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G729" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G730" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G731" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G732" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G733" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G734" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G735" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G736" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G737" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G738" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G739" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G740" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G741" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G742" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G743" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G744" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G745" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G746" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G747" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G748" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G749" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G750" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G751" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G752" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G753" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G754" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G755" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G756" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -4,16 +4,26 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6465" tabRatio="815"/>
+    <workbookView xWindow="5625" yWindow="3825" windowWidth="20730" windowHeight="11145" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="totalDetected1">'Rif Resistance Report'!$E$8</definedName>
     <definedName name="totalDetected2" localSheetId="0">'Rif Resistance Report'!$G$8</definedName>
+    <definedName name="totalDetected2">'Rif Resistance Report'!$F$8</definedName>
   </definedNames>
   <calcPr calcId="144525" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" Flags="2"/>
     </ext>
@@ -22,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Total Tests</t>
   </si>
@@ -76,13 +86,16 @@
   </si>
   <si>
     <t>&lt;totalDetected1&gt;</t>
+  </si>
+  <si>
+    <t>&lt;rifResistanceRate&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -121,6 +134,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -187,7 +207,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -231,8 +251,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -248,12 +269,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="43" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -297,6 +323,7 @@
     <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="43" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -639,7 +666,7 @@
     <col min="1" max="3" width="27.125" customWidth="1"/>
     <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
     <col min="5" max="6" width="14.875" customWidth="1"/>
-    <col min="7" max="7" width="17.75" customWidth="1"/>
+    <col min="7" max="7" width="17.625" style="9" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -674,28 +701,28 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -718,9 +745,8 @@
       <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7" t="e">
-        <f t="shared" ref="G8" si="0">IF(F8=0,0,E8/F8)</f>
-        <v>#VALUE!</v>
+      <c r="G8" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -263,21 +263,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="43" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -663,10 +663,13 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="27.125" customWidth="1"/>
+    <col min="1" max="1" width="39.125" customWidth="1"/>
+    <col min="2" max="2" width="29.125" customWidth="1"/>
+    <col min="3" max="3" width="27.125" customWidth="1"/>
     <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
-    <col min="5" max="6" width="14.875" customWidth="1"/>
-    <col min="7" max="7" width="17.625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -701,28 +704,27 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:7" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:7" s="11" customFormat="1" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -739,10 +741,10 @@
       <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="8" t="s">

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\rif_resistance_rate\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="5625" yWindow="3825" windowWidth="20730" windowHeight="11145" tabRatio="815"/>
   </bookViews>
@@ -14,7 +19,7 @@
     <definedName name="totalDetected2" localSheetId="0">'Rif Resistance Report'!$G$8</definedName>
     <definedName name="totalDetected2">'Rif Resistance Report'!$F$8</definedName>
   </definedNames>
-  <calcPr calcId="144525" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="144525" fullPrecision="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -94,7 +99,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -253,7 +258,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -266,17 +271,27 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -666,10 +681,10 @@
     <col min="1" max="1" width="39.125" customWidth="1"/>
     <col min="2" max="2" width="29.125" customWidth="1"/>
     <col min="3" max="3" width="27.125" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -705,17 +720,17 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:7" s="11" customFormat="1" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -724,7 +739,7 @@
       <c r="F7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="13" t="s">
         <v>4</v>
       </c>
     </row>
@@ -738,16 +753,16 @@
       <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>18</v>
       </c>
     </row>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\rif_resistance_rate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nicolas\Trabajo\SystemOne\Repositorios\Aspect2\aspect\api\templates\rif_resistance_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F91E0D-38C4-444E-BB4E-4C058F5CDCC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5625" yWindow="3825" windowWidth="20730" windowHeight="11145" tabRatio="815"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
@@ -21,14 +22,6 @@
   </definedNames>
   <calcPr calcId="144525" fullPrecision="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" Flags="2"/>
     </ext>
@@ -54,24 +47,9 @@
     <t>RIF Resistance Rate</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>County</t>
-  </si>
-  <si>
-    <t>Devices</t>
-  </si>
-  <si>
     <t>Date Range: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>LGA: &lt;Lgas&gt;</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -94,12 +72,27 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>&lt;State_Label&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Lga_Label&gt;</t>
+  </si>
+  <si>
+    <t>&lt;State_Label&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Lga_Label&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -674,7 +667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -684,7 +677,7 @@
     <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -699,22 +692,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -722,13 +715,13 @@
     </row>
     <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>0</v>
@@ -745,25 +738,25 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nicolas\Trabajo\SystemOne\Repositorios\Aspect2\aspect\api\templates\rif_resistance_rate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\rif_resistance_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F91E0D-38C4-444E-BB4E-4C058F5CDCC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5625" yWindow="3825" windowWidth="20730" windowHeight="11145" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
@@ -22,6 +21,14 @@
   </definedNames>
   <calcPr calcId="144525" fullPrecision="0"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" Flags="2"/>
     </ext>
@@ -47,9 +54,24 @@
     <t>RIF Resistance Rate</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Devices</t>
+  </si>
+  <si>
     <t>Date Range: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t>States: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>LGA: &lt;Lgas&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -72,27 +94,12 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
-  </si>
-  <si>
-    <t>Device</t>
-  </si>
-  <si>
-    <t>&lt;State_Label&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Lga_Label&gt;</t>
-  </si>
-  <si>
-    <t>&lt;State_Label&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Lga_Label&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -667,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -677,7 +684,7 @@
     <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -692,22 +699,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -715,13 +722,13 @@
     </row>
     <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>0</v>
@@ -738,25 +745,25 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\rif_resistance_rate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\rif_resistance_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF5C8CE-AF96-4FE5-ACA2-F9844A4CADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5625" yWindow="3825" windowWidth="20730" windowHeight="11145" tabRatio="815"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
@@ -21,14 +22,6 @@
   </definedNames>
   <calcPr calcId="144525" fullPrecision="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" Flags="2"/>
     </ext>
@@ -45,15 +38,6 @@
     <t>RIF Resistance Report</t>
   </si>
   <si>
-    <t>Total Result1 Positive</t>
-  </si>
-  <si>
-    <t>Total Result2 Negative</t>
-  </si>
-  <si>
-    <t>RIF Resistance Rate</t>
-  </si>
-  <si>
     <t>State</t>
   </si>
   <si>
@@ -94,12 +78,21 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
+  </si>
+  <si>
+    <t>MTB Detected</t>
+  </si>
+  <si>
+    <t>Rif Resistance Detected</t>
+  </si>
+  <si>
+    <t>Rif Resistance Rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -674,96 +667,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.125" customWidth="1"/>
-    <col min="2" max="2" width="29.125" customWidth="1"/>
-    <col min="3" max="3" width="27.125" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="39.09765625" customWidth="1"/>
+    <col min="2" max="2" width="29.09765625" customWidth="1"/>
+    <col min="3" max="3" width="27.09765625" customWidth="1"/>
+    <col min="4" max="4" width="12.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.3984375" customWidth="1"/>
+    <col min="9" max="9" width="14.3984375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\rif_resistance_rate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\rif_resistance_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF5C8CE-AF96-4FE5-ACA2-F9844A4CADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
@@ -38,12 +37,6 @@
     <t>RIF Resistance Report</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>County</t>
-  </si>
-  <si>
     <t>Devices</t>
   </si>
   <si>
@@ -87,12 +80,18 @@
   </si>
   <si>
     <t>Rif Resistance Rate</t>
+  </si>
+  <si>
+    <t>&lt;CountyLabel&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StateLabel&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -333,8 +332,36 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="43" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -667,7 +694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -692,22 +719,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -715,48 +742,48 @@
     </row>
     <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -43,12 +43,6 @@
     <t>Date Range: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>LGA: &lt;Lgas&gt;</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -86,6 +80,12 @@
   </si>
   <si>
     <t>&lt;StateLabel&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
@@ -724,17 +724,17 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -745,45 +745,45 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF0E4568-CA38-8D49-8030-E5208733C990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Rif Resistance Report" state="visible" r:id="rId4"/>
+    <sheet name="Rif Resistance Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="totalDetected1">'Rif Resistance Report'!$E$9</definedName>
     <definedName name="totalDetected2">'Rif Resistance Report'!$G$9</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -38,9 +40,6 @@
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>Devices</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
@@ -84,41 +83,44 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
+  </si>
+  <si>
+    <t>Device</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -144,24 +146,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -171,40 +195,40 @@
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -223,121 +247,432 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.015625" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.1" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="29.1" customWidth="1"/>
-    <col min="4" max="4" width="27.1" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.89" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.6" customWidth="1"/>
-    <col min="9" max="9" width="14.4" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="15.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="G10" s="1"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="G11" s="1"/>
       <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF0E4568-CA38-8D49-8030-E5208733C990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Rif Resistance Report" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Rif Resistance Report" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="totalDetected1">'Rif Resistance Report'!$E$9</definedName>
     <definedName name="totalDetected2">'Rif Resistance Report'!$G$9</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>RIF Resistance Report</t>
   </si>
@@ -37,12 +35,18 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
     <t>Site</t>
   </si>
   <si>
+    <t>Device</t>
+  </si>
+  <si>
     <t>&lt;StateLabel&gt;</t>
   </si>
   <si>
@@ -61,12 +65,12 @@
     <t>Rif Resistance Rate</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
     <t>&lt;state&gt;</t>
   </si>
   <si>
@@ -83,44 +87,41 @@
   </si>
   <si>
     <t>&lt;rifResistanceRate&gt;</t>
-  </si>
-  <si>
-    <t>Device</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -146,46 +147,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -563,9 +542,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="39.1640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -579,100 +558,105 @@
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33.75" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="H9" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G10" s="1"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" ht="16" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G11" s="1"/>
       <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -182,9 +182,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>

--- a/api/templates/rif_resistance_rate/en.xlsx
+++ b/api/templates/rif_resistance_rate/en.xlsx
@@ -35,7 +35,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
